--- a/rules/CORE-000179/negative/02/data/unit-test-coreid-CG0307-negative-02.xlsx
+++ b/rules/CORE-000179/negative/02/data/unit-test-coreid-CG0307-negative-02.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Validation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ts.xpt" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Library" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ts.xpt" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -40,7 +40,7 @@
       <sz val="9.5"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -63,6 +63,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -108,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -127,6 +133,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -570,38 +579,152 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Error group</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Error level</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Row num</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Error value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ts.xpt</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TSPARM</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Planned Maximum Age of
+Subjects</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ts.xpt</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>TSPARMCD</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>AGEMAX</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ts.xpt</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TSPARM</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Planned Maximum Age of
+Subjects</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ts.xpt</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>TSPARMCD</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>AGEMIN</t>
         </is>
       </c>
     </row>
@@ -838,22 +961,22 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -888,7 +1011,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -939,7 +1062,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -972,12 +1095,12 @@
       <c r="C8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>AGEMAX</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>Planned Maximum Age of
 Subjects</t>
@@ -995,7 +1118,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -1005,7 +1128,7 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1023,12 +1146,12 @@
       <c r="C9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>AGEMIN</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>Planned Maximum Age of
 Subjects</t>
@@ -1041,12 +1164,12 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -1056,7 +1179,7 @@
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1091,7 +1214,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
@@ -1104,7 +1227,7 @@
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1139,12 +1262,12 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -1154,7 +1277,7 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1189,22 +1312,22 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1239,22 +1362,22 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1289,7 +1412,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1339,7 +1462,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1389,7 +1512,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1439,12 +1562,12 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -1489,7 +1612,7 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1539,7 +1662,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1589,22 +1712,22 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1639,7 +1762,7 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1690,7 +1813,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1740,7 +1863,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1790,7 +1913,7 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1840,7 +1963,7 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -1890,7 +2013,7 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -1940,7 +2063,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -1990,7 +2113,7 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
